--- a/astro-site/public/dl/guia-restaurante-peruano/checklist-appcc.xlsx
+++ b/astro-site/public/dl/guia-restaurante-peruano/checklist-appcc.xlsx
@@ -11,6 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$4:$H$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +490,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -518,6 +519,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1730,6 +1732,7 @@
       </c>
       <c r="H43" s="6" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
@@ -1740,8 +1743,8 @@
   </sheetData>
   <autoFilter ref="A4:H4"/>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
@@ -1749,6 +1752,15 @@
       <formula1>"Pendiente,En Curso,Completado"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>